--- a/main/StructureDefinition-bc-patient.xlsx
+++ b/main/StructureDefinition-bc-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4872" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="748">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>Patient.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
+    <t>official | secondary</t>
   </si>
   <si>
     <t>The purpose of this identifier.</t>
@@ -685,10 +685,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+    <t>https://terminology.hlth.gov.bc.ca/ClientRegistry/ValueSet/bc-identifier-use-value-set</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -879,6 +876,15 @@
   </si>
   <si>
     <t>Patient.identifier:JHN.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Patient.identifier:JHN.type</t>
@@ -1215,7 +1221,7 @@
     <t>Patient.telecom.value</t>
   </si>
   <si>
-    <t>The actual contact point details</t>
+    <t>International: +ICC&lt;space&gt;areacode&lt;space&gt;phonenumber Example: +1 302 1234567, National: areacode&lt;space&gt;phonenumber Example: 2501234567, Email: email@domain</t>
   </si>
   <si>
     <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
@@ -4235,7 +4241,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
@@ -4818,7 +4824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>197</v>
       </c>
@@ -4935,7 +4941,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>202</v>
       </c>
@@ -5119,29 +5125,27 @@
       <c r="X21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="Y21" t="s" s="2">
+      <c r="Y21" s="2"/>
+      <c r="Z21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="Z21" t="s" s="2">
+      <c r="AA21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5156,7 +5160,7 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
@@ -5173,10 +5177,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5199,19 +5203,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5236,31 +5240,31 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5279,7 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
@@ -5284,7 +5288,7 @@
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5292,10 +5296,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5321,16 +5325,16 @@
         <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5343,43 +5347,43 @@
         <v>80</v>
       </c>
       <c r="T23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5394,16 +5398,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5411,10 +5415,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5440,13 +5444,13 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5460,43 +5464,43 @@
         <v>80</v>
       </c>
       <c r="T24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5511,16 +5515,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5528,10 +5532,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5554,16 +5558,16 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5613,7 +5617,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5625,19 +5629,19 @@
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -5645,10 +5649,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5671,16 +5675,16 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5730,7 +5734,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5742,19 +5746,19 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -5762,13 +5766,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
@@ -5793,10 +5797,10 @@
         <v>180</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -5881,7 +5885,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>189</v>
@@ -5996,7 +6000,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>194</v>
@@ -6113,13 +6117,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>135</v>
@@ -6141,16 +6145,16 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6232,7 +6236,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>207</v>
@@ -6261,7 +6265,7 @@
         <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>209</v>
@@ -6298,28 +6302,28 @@
         <v>212</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6334,7 +6338,7 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
@@ -6351,10 +6355,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6377,19 +6381,19 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="N32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -6399,7 +6403,7 @@
         <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>80</v>
@@ -6414,31 +6418,31 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AA32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6453,7 +6457,7 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -6462,7 +6466,7 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6470,10 +6474,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6499,16 +6503,16 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -6521,43 +6525,43 @@
         <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6572,16 +6576,16 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6589,10 +6593,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6618,13 +6622,13 @@
         <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6638,43 +6642,43 @@
         <v>80</v>
       </c>
       <c r="T34" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6689,16 +6693,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6706,10 +6710,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6732,16 +6736,16 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6791,7 +6795,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6803,19 +6807,19 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AK35" t="s" s="2">
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6823,10 +6827,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6849,16 +6853,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6908,7 +6912,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6920,19 +6924,19 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AK36" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AK36" t="s" s="2">
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6940,10 +6944,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6966,70 +6970,70 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="R37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q37" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="R37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -7044,13 +7048,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -7059,12 +7063,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7087,19 +7091,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -7148,7 +7152,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7160,19 +7164,19 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7180,10 +7184,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7295,10 +7299,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7410,12 +7414,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>198</v>
@@ -7529,10 +7533,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7558,16 +7562,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7596,7 +7600,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -7614,7 +7618,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7629,7 +7633,7 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
@@ -7638,7 +7642,7 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7646,10 +7650,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7675,16 +7679,16 @@
         <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7733,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7748,7 +7752,7 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
@@ -7757,7 +7761,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7765,14 +7769,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7794,13 +7798,13 @@
         <v>190</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7850,7 +7854,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7865,7 +7869,7 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>80</v>
@@ -7874,7 +7878,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7882,14 +7886,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7911,13 +7915,13 @@
         <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7967,7 +7971,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7982,7 +7986,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
@@ -7991,7 +7995,7 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7999,10 +8003,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8028,13 +8032,13 @@
         <v>190</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8084,7 +8088,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -8099,7 +8103,7 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
@@ -8108,7 +8112,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -8116,10 +8120,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8145,13 +8149,13 @@
         <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8201,7 +8205,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8216,7 +8220,7 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -8225,7 +8229,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8233,10 +8237,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8259,19 +8263,19 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8320,7 +8324,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8332,10 +8336,10 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>80</v>
@@ -8344,18 +8348,18 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8378,19 +8382,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8439,7 +8443,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8451,19 +8455,19 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8471,10 +8475,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8586,10 +8590,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8701,12 +8705,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>198</v>
@@ -8820,10 +8824,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8849,13 +8853,13 @@
         <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8885,7 +8889,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8903,7 +8907,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8912,13 +8916,13 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
@@ -8927,7 +8931,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8935,10 +8939,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8964,16 +8968,16 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -9022,7 +9026,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9037,7 +9041,7 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
@@ -9046,7 +9050,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -9054,10 +9058,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9083,16 +9087,16 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9121,7 +9125,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -9139,7 +9143,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9154,7 +9158,7 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
@@ -9163,7 +9167,7 @@
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9171,10 +9175,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9197,16 +9201,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9256,7 +9260,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9288,10 +9292,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9314,16 +9318,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9373,7 +9377,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9385,10 +9389,10 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
@@ -9403,12 +9407,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9434,16 +9438,16 @@
         <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9471,10 +9475,10 @@
         <v>212</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -9492,7 +9496,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9510,13 +9514,13 @@
         <v>162</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -9524,10 +9528,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9553,10 +9557,10 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9639,10 +9643,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9668,10 +9672,10 @@
         <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9750,15 +9754,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>80</v>
@@ -9867,12 +9871,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>198</v>
@@ -9984,15 +9988,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>80</v>
@@ -10014,13 +10018,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10103,10 +10107,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10132,10 +10136,10 @@
         <v>190</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10186,7 +10190,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10216,12 +10220,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10244,19 +10248,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10305,7 +10309,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10320,27 +10324,27 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10366,10 +10370,10 @@
         <v>190</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10452,10 +10456,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10481,10 +10485,10 @@
         <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10565,13 +10569,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>80</v>
@@ -10680,12 +10684,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>198</v>
@@ -10797,15 +10801,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>80</v>
@@ -10827,13 +10831,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10916,10 +10920,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10942,13 +10946,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10999,7 +11003,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11029,12 +11033,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11057,19 +11061,19 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -11118,7 +11122,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11133,7 +11137,7 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>109</v>
@@ -11142,7 +11146,7 @@
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -11150,10 +11154,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11179,10 +11183,10 @@
         <v>190</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11265,10 +11269,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11294,10 +11298,10 @@
         <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11376,15 +11380,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>80</v>
@@ -11493,12 +11497,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>198</v>
@@ -11610,15 +11614,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>80</v>
@@ -11640,13 +11644,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11727,15 +11731,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>80</v>
@@ -11757,13 +11761,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11846,10 +11850,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11872,13 +11876,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11929,7 +11933,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11959,12 +11963,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11987,19 +11991,19 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12048,7 +12052,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12063,16 +12067,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12080,10 +12084,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12195,10 +12199,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12312,10 +12316,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>115</v>
@@ -12340,13 +12344,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>139</v>
@@ -12431,13 +12435,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>135</v>
@@ -12459,16 +12463,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12548,12 +12552,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>198</v>
@@ -12665,15 +12669,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>80</v>
@@ -12695,13 +12699,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12784,10 +12788,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12813,16 +12817,16 @@
         <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12835,7 +12839,7 @@
         <v>80</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>80</v>
@@ -12850,10 +12854,10 @@
         <v>212</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12871,7 +12875,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12886,7 +12890,7 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -12895,7 +12899,7 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12903,10 +12907,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12932,13 +12936,13 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12952,7 +12956,7 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>80</v>
@@ -12967,10 +12971,10 @@
         <v>212</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12988,7 +12992,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13003,7 +13007,7 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>80</v>
@@ -13012,7 +13016,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13020,10 +13024,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13049,16 +13053,16 @@
         <v>190</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13071,7 +13075,7 @@
         <v>80</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>80</v>
@@ -13107,7 +13111,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13122,7 +13126,7 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>80</v>
@@ -13131,7 +13135,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13139,10 +13143,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13168,13 +13172,13 @@
         <v>190</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13188,7 +13192,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13224,7 +13228,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13239,7 +13243,7 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>80</v>
@@ -13248,7 +13252,7 @@
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13256,14 +13260,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13285,13 +13289,13 @@
         <v>190</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13305,7 +13309,7 @@
         <v>80</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>80</v>
@@ -13341,7 +13345,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13356,7 +13360,7 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>80</v>
@@ -13365,7 +13369,7 @@
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13373,14 +13377,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13402,13 +13406,13 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13422,7 +13426,7 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>80</v>
@@ -13458,7 +13462,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13473,7 +13477,7 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>80</v>
@@ -13482,7 +13486,7 @@
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13490,14 +13494,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13519,13 +13523,13 @@
         <v>190</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13575,7 +13579,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13590,7 +13594,7 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
@@ -13599,7 +13603,7 @@
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13607,14 +13611,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13636,13 +13640,13 @@
         <v>190</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13656,7 +13660,7 @@
         <v>80</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>80</v>
@@ -13692,7 +13696,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13707,7 +13711,7 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -13716,7 +13720,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13724,10 +13728,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13753,13 +13757,13 @@
         <v>190</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13809,7 +13813,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13824,7 +13828,7 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -13833,7 +13837,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13841,10 +13845,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13867,19 +13871,19 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13892,7 +13896,7 @@
         <v>80</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>80</v>
@@ -13928,7 +13932,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13940,10 +13944,10 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>80</v>
@@ -13952,7 +13956,7 @@
         <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -13960,10 +13964,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13986,19 +13990,19 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -14023,13 +14027,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -14047,7 +14051,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14062,16 +14066,16 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -14079,10 +14083,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14105,19 +14109,19 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -14166,7 +14170,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14181,7 +14185,7 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>109</v>
@@ -14190,7 +14194,7 @@
         <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14198,10 +14202,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14313,10 +14317,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14428,15 +14432,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>80</v>
@@ -14545,12 +14549,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>198</v>
@@ -14662,15 +14666,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>80</v>
@@ -14692,13 +14696,13 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14781,10 +14785,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14807,19 +14811,19 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14868,7 +14872,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14880,10 +14884,10 @@
         <v>100</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14892,7 +14896,7 @@
         <v>80</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14900,10 +14904,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14926,19 +14930,19 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14987,7 +14991,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14999,10 +15003,10 @@
         <v>100</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>109</v>
@@ -15019,10 +15023,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15134,10 +15138,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15251,14 +15255,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15280,10 +15284,10 @@
         <v>136</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>139</v>
@@ -15338,7 +15342,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15370,10 +15374,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15396,19 +15400,19 @@
         <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15433,13 +15437,13 @@
         <v>80</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -15457,7 +15461,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15472,7 +15476,7 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>109</v>
@@ -15481,7 +15485,7 @@
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15489,10 +15493,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15515,19 +15519,19 @@
         <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -15576,7 +15580,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15591,7 +15595,7 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>109</v>
@@ -15600,7 +15604,7 @@
         <v>80</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>80</v>
@@ -15608,10 +15612,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15634,19 +15638,19 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
@@ -15695,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15707,10 +15711,10 @@
         <v>100</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>109</v>
@@ -15719,7 +15723,7 @@
         <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15727,10 +15731,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15753,19 +15757,19 @@
         <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -15814,7 +15818,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15829,7 +15833,7 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15838,7 +15842,7 @@
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -15846,10 +15850,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15875,16 +15879,16 @@
         <v>111</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -15912,10 +15916,10 @@
         <v>212</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -15933,7 +15937,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15957,7 +15961,7 @@
         <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -15965,10 +15969,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15991,19 +15995,19 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16052,7 +16056,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16061,13 +16065,13 @@
         <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>109</v>
@@ -16076,7 +16080,7 @@
         <v>80</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16084,10 +16088,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16110,16 +16114,16 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16169,7 +16173,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16181,10 +16185,10 @@
         <v>100</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>109</v>
@@ -16193,7 +16197,7 @@
         <v>80</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16201,10 +16205,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16227,19 +16231,19 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
@@ -16288,7 +16292,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16303,10 +16307,10 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>80</v>
@@ -16320,10 +16324,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16435,10 +16439,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16552,14 +16556,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16581,10 +16585,10 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>139</v>
@@ -16639,7 +16643,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16671,10 +16675,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16697,19 +16701,19 @@
         <v>80</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -16758,7 +16762,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>88</v>
@@ -16773,16 +16777,16 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>80</v>
@@ -16790,10 +16794,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16816,19 +16820,19 @@
         <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -16877,7 +16881,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16892,16 +16896,16 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>80</v>
@@ -16909,14 +16913,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16935,16 +16939,16 @@
         <v>80</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16994,7 +16998,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17006,10 +17010,10 @@
         <v>100</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>109</v>
@@ -17018,7 +17022,7 @@
         <v>80</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>80</v>
@@ -17026,10 +17030,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17052,19 +17056,19 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17113,7 +17117,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17125,13 +17129,13 @@
         <v>100</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>80</v>
@@ -17143,12 +17147,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17171,19 +17175,19 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17232,7 +17236,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17247,7 +17251,7 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>109</v>
@@ -17264,10 +17268,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17379,10 +17383,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17494,15 +17498,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>80</v>
@@ -17524,13 +17528,13 @@
         <v>80</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17613,14 +17617,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17642,10 +17646,10 @@
         <v>136</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>139</v>
@@ -17700,7 +17704,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17732,10 +17736,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17758,16 +17762,16 @@
         <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17817,7 +17821,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>88</v>
@@ -17829,7 +17833,7 @@
         <v>100</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>185</v>
@@ -17841,7 +17845,7 @@
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>80</v>
@@ -17849,10 +17853,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17878,13 +17882,13 @@
         <v>111</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17913,28 +17917,28 @@
         <v>212</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF130" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>88</v>
@@ -17949,7 +17953,7 @@
         <v>101</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>109</v>
@@ -17966,12 +17970,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO130">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
